--- a/Excel/TaskConfig.xlsx
+++ b/Excel/TaskConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
   <si>
     <t>_id</t>
   </si>
@@ -143,37 +143,97 @@
     <t>闯过第500关</t>
   </si>
   <si>
+    <t>闯过1w关</t>
+  </si>
+  <si>
+    <t>闯过2w关</t>
+  </si>
+  <si>
+    <t>闯过3w关</t>
+  </si>
+  <si>
+    <t>闯过4w关</t>
+  </si>
+  <si>
+    <t>闯过5w关</t>
+  </si>
+  <si>
+    <t>闯过6w关</t>
+  </si>
+  <si>
+    <t>闯过7w关</t>
+  </si>
+  <si>
+    <t>闯过8w关</t>
+  </si>
+  <si>
+    <t>闯过9w关</t>
+  </si>
+  <si>
     <t>闯过10w关</t>
   </si>
   <si>
-    <t>闯过20w关</t>
-  </si>
-  <si>
-    <t>闯过30w关</t>
-  </si>
-  <si>
-    <t>闯过40w关</t>
-  </si>
-  <si>
-    <t>闯过50w关</t>
-  </si>
-  <si>
-    <t>闯过60w关</t>
-  </si>
-  <si>
-    <t>闯过70w关</t>
-  </si>
-  <si>
-    <t>闯过80w关</t>
-  </si>
-  <si>
-    <t>闯过90w关</t>
-  </si>
-  <si>
-    <t>闯过100w关</t>
-  </si>
-  <si>
     <t>设置-其他界面，绑定帐号并且存档</t>
+  </si>
+  <si>
+    <t>轮回1转(12w级开启)</t>
+  </si>
+  <si>
+    <t>轮回2转(13w级开启)</t>
+  </si>
+  <si>
+    <t>轮回3转(14w级开启)</t>
+  </si>
+  <si>
+    <t>轮回4转(15w级开启)</t>
+  </si>
+  <si>
+    <t>轮回5转</t>
+  </si>
+  <si>
+    <t>轮回6转</t>
+  </si>
+  <si>
+    <t>轮回7转</t>
+  </si>
+  <si>
+    <t>轮回8转</t>
+  </si>
+  <si>
+    <t>轮回9转</t>
+  </si>
+  <si>
+    <t>轮回10转</t>
+  </si>
+  <si>
+    <t>修炼练气</t>
+  </si>
+  <si>
+    <t>修炼筑基</t>
+  </si>
+  <si>
+    <t>修炼金丹</t>
+  </si>
+  <si>
+    <t>修炼元婴</t>
+  </si>
+  <si>
+    <t>修炼化神</t>
+  </si>
+  <si>
+    <t>修炼练虚</t>
+  </si>
+  <si>
+    <t>修炼合体</t>
+  </si>
+  <si>
+    <t>修炼大乘</t>
+  </si>
+  <si>
+    <t>修炼渡劫</t>
+  </si>
+  <si>
+    <t>修炼散仙</t>
   </si>
 </sst>
 </file>
@@ -186,7 +246,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,6 +265,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -687,142 +753,143 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1142,8 +1209,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="C3:L47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="11.875" style="1" customWidth="1"/>
@@ -1152,12 +1219,12 @@
     <col min="7" max="7" width="17.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="13.75" style="1" customWidth="1"/>
     <col min="9" max="10" width="12.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.625" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:12">
+    <row r="3" ht="13.5" spans="3:12">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1189,7 +1256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="3:12">
+    <row r="4" ht="13.5" spans="3:12">
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1221,7 +1288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="3:12">
+    <row r="5" ht="13.5" spans="3:12">
       <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1577,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="1">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1609,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="1">
-        <v>200000</v>
+        <v>20000</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1641,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="1">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1673,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1">
-        <v>400000</v>
+        <v>40000</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1705,7 +1772,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="1">
-        <v>500000</v>
+        <v>50000</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1737,7 +1804,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="1">
-        <v>600000</v>
+        <v>60000</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1769,7 +1836,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="1">
-        <v>700000</v>
+        <v>70000</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -1801,7 +1868,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="1">
-        <v>800000</v>
+        <v>80000</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -1833,7 +1900,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="1">
-        <v>900000</v>
+        <v>90000</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -1865,7 +1932,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="1">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -1921,9 +1988,649 @@
         <v>12</v>
       </c>
     </row>
+    <row r="28" spans="3:12">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1">
+        <v>8</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I28" s="3">
+        <v>15</v>
+      </c>
+      <c r="J28" s="1">
+        <v>20</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L28" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <v>8</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I29" s="3">
+        <v>15</v>
+      </c>
+      <c r="J29" s="1">
+        <v>20</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L29" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1">
+        <v>8</v>
+      </c>
+      <c r="E30" s="1">
+        <v>3</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I30" s="3">
+        <v>15</v>
+      </c>
+      <c r="J30" s="1">
+        <v>20</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L30" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <v>8</v>
+      </c>
+      <c r="E31" s="1">
+        <v>4</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I31" s="3">
+        <v>15</v>
+      </c>
+      <c r="J31" s="1">
+        <v>20</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L31" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12">
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1">
+        <v>8</v>
+      </c>
+      <c r="E32" s="1">
+        <v>5</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I32" s="3">
+        <v>15</v>
+      </c>
+      <c r="J32" s="1">
+        <v>20</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L32" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="3:12">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1">
+        <v>8</v>
+      </c>
+      <c r="E33" s="1">
+        <v>6</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I33" s="3">
+        <v>15</v>
+      </c>
+      <c r="J33" s="1">
+        <v>20</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L33" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="3:12">
+      <c r="C34" s="1">
+        <v>29</v>
+      </c>
+      <c r="D34" s="1">
+        <v>8</v>
+      </c>
+      <c r="E34" s="1">
+        <v>7</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I34" s="3">
+        <v>15</v>
+      </c>
+      <c r="J34" s="1">
+        <v>20</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L34" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="3:12">
+      <c r="C35" s="1">
+        <v>30</v>
+      </c>
+      <c r="D35" s="1">
+        <v>8</v>
+      </c>
+      <c r="E35" s="1">
+        <v>8</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I35" s="3">
+        <v>15</v>
+      </c>
+      <c r="J35" s="1">
+        <v>20</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L35" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="3:12">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1">
+        <v>8</v>
+      </c>
+      <c r="E36" s="1">
+        <v>9</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I36" s="3">
+        <v>15</v>
+      </c>
+      <c r="J36" s="1">
+        <v>20</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L36" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="3:12">
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1">
+        <v>8</v>
+      </c>
+      <c r="E37" s="1">
+        <v>10</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I37" s="3">
+        <v>15</v>
+      </c>
+      <c r="J37" s="1">
+        <v>30</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L37" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="3:12">
+      <c r="C38" s="1">
+        <v>33</v>
+      </c>
+      <c r="D38" s="1">
+        <v>8</v>
+      </c>
+      <c r="E38" s="1">
+        <v>11</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I38" s="3">
+        <v>15</v>
+      </c>
+      <c r="J38" s="1">
+        <v>30</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L38" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="3:12">
+      <c r="C39" s="1">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1">
+        <v>8</v>
+      </c>
+      <c r="E39" s="1">
+        <v>12</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I39" s="3">
+        <v>15</v>
+      </c>
+      <c r="J39" s="1">
+        <v>30</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L39" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="3:12">
+      <c r="C40" s="1">
+        <v>35</v>
+      </c>
+      <c r="D40" s="1">
+        <v>8</v>
+      </c>
+      <c r="E40" s="1">
+        <v>13</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I40" s="3">
+        <v>15</v>
+      </c>
+      <c r="J40" s="1">
+        <v>30</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="3:12">
+      <c r="C41" s="1">
+        <v>36</v>
+      </c>
+      <c r="D41" s="1">
+        <v>8</v>
+      </c>
+      <c r="E41" s="1">
+        <v>14</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I41" s="3">
+        <v>15</v>
+      </c>
+      <c r="J41" s="1">
+        <v>30</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L41" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="3:12">
+      <c r="C42" s="1">
+        <v>37</v>
+      </c>
+      <c r="D42" s="1">
+        <v>8</v>
+      </c>
+      <c r="E42" s="1">
+        <v>15</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I42" s="3">
+        <v>15</v>
+      </c>
+      <c r="J42" s="1">
+        <v>30</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L42" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="3:12">
+      <c r="C43" s="1">
+        <v>38</v>
+      </c>
+      <c r="D43" s="1">
+        <v>8</v>
+      </c>
+      <c r="E43" s="1">
+        <v>16</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I43" s="3">
+        <v>15</v>
+      </c>
+      <c r="J43" s="1">
+        <v>30</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L43" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="3:12">
+      <c r="C44" s="1">
+        <v>39</v>
+      </c>
+      <c r="D44" s="1">
+        <v>8</v>
+      </c>
+      <c r="E44" s="1">
+        <v>17</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I44" s="3">
+        <v>15</v>
+      </c>
+      <c r="J44" s="1">
+        <v>30</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L44" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="3:12">
+      <c r="C45" s="1">
+        <v>40</v>
+      </c>
+      <c r="D45" s="1">
+        <v>8</v>
+      </c>
+      <c r="E45" s="1">
+        <v>18</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I45" s="3">
+        <v>15</v>
+      </c>
+      <c r="J45" s="1">
+        <v>30</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L45" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="3:12">
+      <c r="C46" s="1">
+        <v>41</v>
+      </c>
+      <c r="D46" s="1">
+        <v>8</v>
+      </c>
+      <c r="E46" s="1">
+        <v>19</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I46" s="3">
+        <v>15</v>
+      </c>
+      <c r="J46" s="1">
+        <v>30</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L46" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="3:12">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="1">
+        <v>8</v>
+      </c>
+      <c r="E47" s="1">
+        <v>20</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>4020</v>
+      </c>
+      <c r="I47" s="3">
+        <v>15</v>
+      </c>
+      <c r="J47" s="1">
+        <v>30</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L47" s="1">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 H3 I3 J3 K3 L3 D4 E4 F4 G4 H4 I4 J4 K4 L4 D5 E5:F5 G5 H5:I5 J5 K5:L5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
